--- a/Plants Benefits.xlsx
+++ b/Plants Benefits.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="470">
   <si>
     <t>Plant</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Artemisia absinthium</t>
   </si>
   <si>
-    <t>Wormwood is the basis for the famous absinthe drink so dear to the painter Verlaine. The disastrous effect on drinkers of the "green fairy" was said to be the plant's thujone content. However, that the liqueur's toxicity was due to thujone is now contested. The anti-absinthe campaign was in fact orchestrated by French winemakers to bring down this competitor. The aniseed-based aperitifs that took its place contained anethole, a substance whose neurotoxic effects are now widely known. Thujone does give Wormwood essential oil a convulsive and abortive effect.</t>
-  </si>
-  <si>
     <t>Wood Avens</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>Hypericum perforatum</t>
   </si>
   <si>
-    <t>St. John's-wort can decrease the effect of certain oral cardiotonic, antiretroviral, anti-asthmatic and contraceptive medicines when taken simultaneously. The hypericin in St. John's-wort can cause photosensitization, inflammation of the skin when exposed to sun. However, this has not been observed at usual doses of the infusion, as hypericin is not very soluble in water.</t>
-  </si>
-  <si>
     <t>Drosera rotundifolia</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
     <t>Pulsatilla vulgaris</t>
   </si>
   <si>
-    <t>Pasqueflowers are irritants when fresh. Wrongful ingestion could lead to respiratory and heart problems. Use of the plant is not advised during pregnancy: the protoanemonin has been shown to cause abortions or malformations of the embryo in cattle.</t>
-  </si>
-  <si>
     <t>Oregano</t>
   </si>
   <si>
@@ -267,9 +258,6 @@
     <t>Artemisia vulgaris</t>
   </si>
   <si>
-    <t>The use of Mugwort is not recommended during pregnancy. Mugwort pollen is strongly allergenic, but less so than its cousin Ragweed (Ambrosia artemisiifolia).</t>
-  </si>
-  <si>
     <t>Mouse-ear-hawkweed</t>
   </si>
   <si>
@@ -450,9 +438,6 @@
     <t>Fumaria officinalis</t>
   </si>
   <si>
-    <t>Precaution for use: Note that Flax seeds should not be eaten where there is intestinal obstruction or narrowing of the oesophagus or digestive tract. Flax seeds should be taken separately from other medications (by at least 30 minutes to 1 hour). If taking Flax Seeds, it is essential to drink 1 1/2 to 2 liters of water per day.</t>
-  </si>
-  <si>
     <t>Flax</t>
   </si>
   <si>
@@ -607,9 +592,6 @@
   </si>
   <si>
     <t>Symphytum officinale</t>
-  </si>
-  <si>
-    <t>In laboratory experiments, pyrrolizidine alkaloids have caused liver tumours. Although no classified disorders are associated with the plant, its regular use as an infusion is not recommended. It should not be used for more than one month at a stretch. It should not be taken by pregnant women or young children.</t>
   </si>
   <si>
     <t>Colt's-foot</t>
@@ -1180,9 +1162,6 @@
     <t xml:space="preserve">
 If you collect the berries in the wild, make sure you do not confuse Black Elder with Dwarf Elder (Sambucus ebulus), which has poisonous berries.
 Respect the dose of 4 to 8g of berries per day, whatever form they are in. Above this dose, they become purgative.</t>
-  </si>
-  <si>
-    <t>Arnica is far too dangerous to be recommended for internal use. Above 4 to 8g per litre(quart), it can trigger a profound alteration in the nervous system, leading to cold sweats, headaches, abdominal pain, palpitations and breathing problems. There are occasional cases of allergies to Arnica, as well as to other plants in the Asteraceae family. Varieties from the Iberian Peninsula do not contain the allergenic helenalin and are therefore better tolerated.</t>
   </si>
   <si>
     <t>Blackseed (often known as Nigella seeds) promotes digestion and expel gas from the intestines.
@@ -1433,6 +1412,416 @@
 It can also be beneficial in cases of erectile dysfunction.
 The essential oil has anti-infectious properties and stimulates the immune system. It is prescribed for bacterial or parasitic intestinal, pulmonary or cutaneous infections. It is also an antioxidant.
 Winter Savory, along with a number of other aromatic plants, is one of the ingredients of the "vulnerary alcoholate" known as "Arquebusade Water".</t>
+  </si>
+  <si>
+    <t>Alfalfa</t>
+  </si>
+  <si>
+    <t>Aloe</t>
+  </si>
+  <si>
+    <t>Andrographis</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Artichoke</t>
+  </si>
+  <si>
+    <t>Ashwagandha</t>
+  </si>
+  <si>
+    <t>Astragalus</t>
+  </si>
+  <si>
+    <t>Bacopa</t>
+  </si>
+  <si>
+    <t>Barberry</t>
+  </si>
+  <si>
+    <t>Bayberry</t>
+  </si>
+  <si>
+    <t>Bitter Melon</t>
+  </si>
+  <si>
+    <t>Blackberry</t>
+  </si>
+  <si>
+    <t>Black Cohosh</t>
+  </si>
+  <si>
+    <t>Black Haw</t>
+  </si>
+  <si>
+    <t>Boneset</t>
+  </si>
+  <si>
+    <t>Boswellia (Indian Frankincense)</t>
+  </si>
+  <si>
+    <t>Buchu</t>
+  </si>
+  <si>
+    <t>Buckthorn</t>
+  </si>
+  <si>
+    <t>Burdock</t>
+  </si>
+  <si>
+    <t>Butterbur</t>
+  </si>
+  <si>
+    <t>Cannabis (Marijuana)</t>
+  </si>
+  <si>
+    <t>Cascara Sagrada</t>
+  </si>
+  <si>
+    <t>Catnip</t>
+  </si>
+  <si>
+    <t>Cat's Claw</t>
+  </si>
+  <si>
+    <t>Celery</t>
+  </si>
+  <si>
+    <t>Chamomile</t>
+  </si>
+  <si>
+    <t>Chaparral</t>
+  </si>
+  <si>
+    <t>Cinnamon</t>
+  </si>
+  <si>
+    <t>Clove</t>
+  </si>
+  <si>
+    <t>Cocoa (Chocolate)</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Cordyceps</t>
+  </si>
+  <si>
+    <t>Cranberry</t>
+  </si>
+  <si>
+    <t>Dandelion</t>
+  </si>
+  <si>
+    <t>Devil's Claw</t>
+  </si>
+  <si>
+    <t>Dill</t>
+  </si>
+  <si>
+    <t>Echinacea</t>
+  </si>
+  <si>
+    <t>Elderberry</t>
+  </si>
+  <si>
+    <t>Elecampane</t>
+  </si>
+  <si>
+    <t>Eleutherococcus</t>
+  </si>
+  <si>
+    <t>Ephedra</t>
+  </si>
+  <si>
+    <t>Evening Primrose</t>
+  </si>
+  <si>
+    <t>Fenugreek</t>
+  </si>
+  <si>
+    <t>Feverfew</t>
+  </si>
+  <si>
+    <t>Garlic</t>
+  </si>
+  <si>
+    <t>Ginger</t>
+  </si>
+  <si>
+    <t>Ginkgo</t>
+  </si>
+  <si>
+    <t>Ginseng</t>
+  </si>
+  <si>
+    <t>Goldenseal</t>
+  </si>
+  <si>
+    <t>Gotu Kola</t>
+  </si>
+  <si>
+    <t>Hawthorn</t>
+  </si>
+  <si>
+    <t>Hibiscus</t>
+  </si>
+  <si>
+    <t>Hop</t>
+  </si>
+  <si>
+    <t>Horehound</t>
+  </si>
+  <si>
+    <t>Horse Chestnut</t>
+  </si>
+  <si>
+    <t>Horsetail</t>
+  </si>
+  <si>
+    <t>Juniper</t>
+  </si>
+  <si>
+    <t>Kava</t>
+  </si>
+  <si>
+    <t>Kola</t>
+  </si>
+  <si>
+    <t>Kudzu</t>
+  </si>
+  <si>
+    <t>Licorice</t>
+  </si>
+  <si>
+    <t>Maca</t>
+  </si>
+  <si>
+    <t>Maitake</t>
+  </si>
+  <si>
+    <t>Marshmallow</t>
+  </si>
+  <si>
+    <t>Maté</t>
+  </si>
+  <si>
+    <t>Milk Thistle</t>
+  </si>
+  <si>
+    <t>Mistletoe</t>
+  </si>
+  <si>
+    <t>Motherwort</t>
+  </si>
+  <si>
+    <t>Muira Puama</t>
+  </si>
+  <si>
+    <t>Mullein</t>
+  </si>
+  <si>
+    <t>Myrrh</t>
+  </si>
+  <si>
+    <t>Neem</t>
+  </si>
+  <si>
+    <t>Nettle</t>
+  </si>
+  <si>
+    <t>Papaya</t>
+  </si>
+  <si>
+    <t>Parsley</t>
+  </si>
+  <si>
+    <t>Passionflower</t>
+  </si>
+  <si>
+    <t>Pau D'Arco</t>
+  </si>
+  <si>
+    <t>Pelargonium</t>
+  </si>
+  <si>
+    <t>Pennyroyal</t>
+  </si>
+  <si>
+    <t>Peppermint &amp; Spearmint</t>
+  </si>
+  <si>
+    <t>Psyllium</t>
+  </si>
+  <si>
+    <t>Pumpkin Seed</t>
+  </si>
+  <si>
+    <t>Purslane</t>
+  </si>
+  <si>
+    <t>Pygeum</t>
+  </si>
+  <si>
+    <t>Rasberry</t>
+  </si>
+  <si>
+    <t>Red Clover</t>
+  </si>
+  <si>
+    <t>Red pepper</t>
+  </si>
+  <si>
+    <t>Reishi</t>
+  </si>
+  <si>
+    <t>Rhodiola</t>
+  </si>
+  <si>
+    <t>Rhubarb</t>
+  </si>
+  <si>
+    <t>Rooibos</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Saffron</t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t>Sarsaparilla</t>
+  </si>
+  <si>
+    <t>Saw Palmetto</t>
+  </si>
+  <si>
+    <t>Schisandra</t>
+  </si>
+  <si>
+    <t>Scullcap</t>
+  </si>
+  <si>
+    <t>Senna</t>
+  </si>
+  <si>
+    <t>Shiitake</t>
+  </si>
+  <si>
+    <t>Slippery Elm</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>Stevia</t>
+  </si>
+  <si>
+    <t>Tarragon</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>Tea Tree</t>
+  </si>
+  <si>
+    <t>Thyme</t>
+  </si>
+  <si>
+    <t>Turmeric (Curcumin)</t>
+  </si>
+  <si>
+    <t>Uva-Ursi</t>
+  </si>
+  <si>
+    <t>Valerian</t>
+  </si>
+  <si>
+    <t>Vervain</t>
+  </si>
+  <si>
+    <t>White Willow</t>
+  </si>
+  <si>
+    <t>Witch Hazel</t>
+  </si>
+  <si>
+    <t>Yohimbe</t>
+  </si>
+  <si>
+    <t>Arnica is far too dangerous to be recommended for internal use. Above 4 to 8g per litre(quart), it can trigger a profound alteration in the nervous system, leading to cold sweats, headaches, abdominal pain, palpitations and breathing problems. 
+There are occasional cases of allergies to Arnica, as well as to other plants in the Asteraceae family. Varieties from the Iberian Peninsula do not contain the allergenic helenalin and are therefore better tolerated.</t>
+  </si>
+  <si>
+    <t>In laboratory experiments, pyrrolizidine alkaloids have caused liver tumours. Although no classified disorders are associated with the plant, its regular use as an infusion is not recommended. 
+It should not be used for more than one month at a stretch. It should not be taken by pregnant women or young children.</t>
+  </si>
+  <si>
+    <t>Precaution for use: Note that Flax seeds should not be eaten where there is intestinal obstruction or narrowing of the oesophagus or digestive tract. 
+Flax seeds should be taken separately from other medications (by at least 30 minutes to 1 hour). If taking Flax Seeds, it is essential to drink 1 1/2 to 2 liters of water per day.</t>
+  </si>
+  <si>
+    <t>The use of Mugwort is not recommended during pregnancy. 
+Mugwort pollen is strongly allergenic, but less so than its cousin Ragweed (Ambrosia artemisiifolia).</t>
+  </si>
+  <si>
+    <t>Pasqueflowers are irritants when fresh. Wrongful ingestion could lead to respiratory and heart problems. 
+Use of the plant is not advised during pregnancy: the protoanemonin has been shown to cause abortions or malformations of the embryo in cattle.</t>
+  </si>
+  <si>
+    <t>St. John's-wort can decrease the effect of certain oral cardiotonic, antiretroviral, anti-asthmatic and contraceptive medicines when taken simultaneously. 
+The hypericin in St. John's-wort can cause photosensitization, inflammation of the skin when exposed to sun. However, this has not been observed at usual doses of the infusion, as hypericin is not very soluble in water.</t>
+  </si>
+  <si>
+    <t>Wormwood is the basis for the famous absinthe drink so dear to the painter Verlaine. The disastrous effect on drinkers of the "green fairy" was said to be the plant's thujone content.
+However, that the liqueur's toxicity was due to thujone is now contested. The anti-absinthe campaign was in fact orchestrated by French winemakers to bring down this competitor. 
+The aniseed-based aperitifs that took its place contained anethole, a substance whose neurotoxic effects are now widely known. Thujone does give Wormwood essential oil a convulsive and abortive effect.</t>
+  </si>
+  <si>
+    <t>Medicago sativa</t>
+  </si>
+  <si>
+    <t>Most of alfalfa's traditional therapeutic uses have long been disproved. But scientists have discovered and alfalfa benefit our ancestors never dreamed of. This herb helps prevent heart disease, stroke, and cancer, the nation's top three killers.
+Animal studies show that alfalfa leaves and seeds reduce blood cholesterol levels. High cholesterol raises risk for heart attack and most strokes. (Alfalfa sprouts produce a similar, but less pronounced benefit.)
+Scandinavian researchers gave alfalfa seeds (1.5 ounces three times a day) to 15 people with high cholesterol. After 8 weeks, their cholesterol level fell significantly.
+One study suggests that alfalfa helps neutralize cancer-causing substances in the intestine. Another, published in the Journal of the National Cancer Institute, shows that the herb binds carcinogens in the colon and helps speed their elimination.
+Alfalfa seeds contain two compounds, stachydrine and homostachydrine, that promote menstruation. They may also trigger miscarriage. Pregnant women should not eat alfalfa seeds. But women should not consider this herb a reliable contraceptive.
+Alfalfa is rich in the green plant pigment chlorophyll, the active ingredient in most commercial breath fresheners. Sip an alfalfa infusion if you're concerned about bad breath.</t>
+  </si>
+  <si>
+    <t>Wash alfalfa sprouts carefully. They may become contaminated with E. coli or Salmonella bacteria and cause food poisoning.
+Do not consume more than recommended amounts of alfalfa seeds. They contain the potentially toxic amino acid canavanine. According to a report in Lancet, over time, eating large quantities of seeds may cause the reversible blood disorder pancytopenia. This condition impairs infection-fighting white blood cells and platelets, necessary for clotting.
+The canavanine in alfalfa seeds has also been linked to systemic lupus erythematosus, a potentially serious auto-immune disease in people who were in remission, according to the New England Journal of Medicine. Another study shows that the seeds induce lupus in monkeys. If you have lupus or have ever had pancytopenia, do not use alfalfa.
+Pregnant and nursing women should not use alfalfa, except sprouts in salads.
+Do not give alfalfa to children under 2. In older children, adjust the recommended dose based on the child's weight. Give a 50-pound child one-third of the dose a 150-pound adult would take.
+If you're over 65, start with a low dose, and increase only if necessary.
+Inform health professionals of the herbs you use. Problematic herb-drug interactions are possible.
+Alfalfa may cause allergic reactions or other unexpected side effects. If any develop, reduce your dose or stop taking it. 
+If symptoms get worse or persist longer than 2 weeks, consult a health professional.</t>
+  </si>
+  <si>
+    <t>Aloe vera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contemporary herbalists and scientists agree with Dioscorides' 2,000-year-old observation that applied topically, aloe treats wounds.
+Aloe contains compounds: bradykinase, salicylic acid, and magnesium lactate that reduce the pain, inflammation, swelling, and redness of wounds. Scientific evidence of aloe's wound-healing power was first documented in 1935, when an American medical journal reported accelerated healing of X-ray burns with aloe gel scooped from the plant's cut leaves.
+Since then, dozens of studies have supported the herb's ability to stimulate healing of first and second degree burns. Asian researchers analyzed many studies of aloe for wound healing.
+Compared with standard care, the wounds of those using aloe healed significantly faster up to 8 days faster.
+Aloe works best for superficial wounds. In a study published in the Journal of Dermatology and Surgical Oncology, the herb sped the healing of pimples by 3 days compared with standard medical treatment. 
+For deep wounds, however, aloe slows healing. That's what researchers found in a study of aloe treatment of cesarean section incisions. </t>
+  </si>
+  <si>
+    <t>4519035540012483</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1482,6 +1871,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1814,17 +2205,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="77.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="61.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="83" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1837,1377 +2228,1380 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D8" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D9" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="240" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D12" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="240" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="180" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="240" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>197</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="270" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="300" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="285" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>144</v>
+        <v>459</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="315" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>71</v>
+        <v>461</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C84" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>51</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C90" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C97" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C99" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="225" x14ac:dyDescent="0.25">
@@ -3218,10 +3612,10 @@
         <v>7</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>8</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="150" x14ac:dyDescent="0.25">
@@ -3232,10 +3626,700 @@
         <v>5</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="300" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="255" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -3258,12 +4342,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
